--- a/output/laminas_comunales/comunal_s_fonasa_a_2023_maule.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2023_maule.xlsx
@@ -375,376 +375,376 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Empedrado</t>
         </is>
       </c>
       <c r="C2">
-        <v>203162</v>
+        <v>94.4129763130793</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="C3">
-        <v>148027</v>
+        <v>93.93087699266611</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="C4">
-        <v>96763</v>
+        <v>93.88492584944622</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="C5">
-        <v>48545</v>
+        <v>93.68215828854463</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="C6">
-        <v>48201</v>
+        <v>93.67711598746081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="C7">
-        <v>47476</v>
+        <v>93.50742692860565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="C8">
-        <v>47396</v>
+        <v>93.36320358443014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="C9">
-        <v>46893</v>
+        <v>93.28165374677003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="C10">
-        <v>45308</v>
+        <v>93.27634825519915</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="C11">
-        <v>43214</v>
+        <v>93.26743307211902</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="C12">
-        <v>35558</v>
+        <v>93.03561052544202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C13">
-        <v>29883</v>
+        <v>93.02172086883475</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C14">
-        <v>23418</v>
+        <v>92.86528595857875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="C15">
-        <v>21389</v>
+        <v>92.46567879712356</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C16">
-        <v>20005</v>
+        <v>92.32507402212872</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="C17">
-        <v>19550</v>
+        <v>91.88143347312239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="C18">
-        <v>18356</v>
+        <v>91.7524128579405</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="C19">
-        <v>16973</v>
+        <v>91.66121220054981</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C20">
-        <v>15503</v>
+        <v>91.26206546193482</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="C21">
-        <v>12575</v>
+        <v>90.65810728596304</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="C22">
-        <v>11503</v>
+        <v>90.65185495703207</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="C23">
-        <v>11208</v>
+        <v>90.616</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C24">
-        <v>10585</v>
+        <v>90.5708787684413</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="C25">
-        <v>10002</v>
+        <v>90.33068229384679</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C26">
-        <v>9781</v>
+        <v>89.88816057475096</v>
       </c>
     </row>
     <row r="27">
@@ -759,67 +759,67 @@
         </is>
       </c>
       <c r="C27">
-        <v>9729</v>
+        <v>89.6599391761128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Pelluhue</t>
         </is>
       </c>
       <c r="C28">
-        <v>9025</v>
+        <v>89.21014228383801</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="C29">
-        <v>7002</v>
+        <v>88.41648391812865</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="C30">
-        <v>4325</v>
+        <v>87.09776117207497</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="C31">
-        <v>3667</v>
+        <v>85.04273862047603</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
